--- a/build/Caltech.xlsx
+++ b/build/Caltech.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="13"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="30" sheetId="1" state="visible" r:id="rId2"/>
@@ -931,7 +931,7 @@
         <v>-1.71</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>1.657</v>
+        <v>1.697</v>
       </c>
       <c r="D12" s="1" t="n">
         <v>0.0425</v>
@@ -1069,7 +1069,7 @@
         <v>-0.553</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>1.154</v>
+        <v>1.194</v>
       </c>
       <c r="D18" s="1" t="n">
         <v>0.3294</v>
